--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -28,10 +28,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>16763</t>
@@ -43,7 +43,7 @@
     <t>FUTBOL PU FUTURE #5</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>16725</t>
@@ -76,7 +76,7 @@
     <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>16757</t>
@@ -127,7 +127,7 @@
     <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>14375</t>
@@ -1238,7 +1238,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1252,6 +1252,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1294,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1302,13 +1318,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1653,13 +1675,12 @@
   <dimension ref="A1:G199"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1819,7 +1840,7 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2000,10 +2021,10 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2072,7 +2093,7 @@
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2187,7 +2208,7 @@
       <c r="F23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2210,7 +2231,7 @@
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2233,7 +2254,7 @@
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2253,10 +2274,10 @@
       <c r="E26">
         <v>48</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="6">
         <v>1</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2279,7 +2300,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2299,10 +2320,10 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="6">
         <v>1</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2348,7 +2369,7 @@
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2371,7 +2392,7 @@
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2555,7 +2576,7 @@
       <c r="F39" s="4">
         <v>0</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2578,7 +2599,7 @@
       <c r="F40" s="4">
         <v>0</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2598,10 +2619,10 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="6">
         <v>5</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2647,7 +2668,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2693,7 +2714,7 @@
       <c r="F45" s="4">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2716,7 +2737,7 @@
       <c r="F46" s="4">
         <v>0</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2762,7 +2783,7 @@
       <c r="F48" s="4">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2782,10 +2803,10 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="6">
         <v>6</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2831,7 +2852,7 @@
       <c r="F51" s="4">
         <v>0</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2874,10 +2895,10 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="6">
         <v>1</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2992,7 +3013,7 @@
       <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3015,7 +3036,7 @@
       <c r="F59" s="4">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3061,7 +3082,7 @@
       <c r="F61" s="4">
         <v>0</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3314,7 +3335,7 @@
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3518,10 +3539,10 @@
       <c r="E81">
         <v>60</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="6">
         <v>5</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3590,7 +3611,7 @@
       <c r="F84" s="4">
         <v>0</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3682,7 +3703,7 @@
       <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3705,7 +3726,7 @@
       <c r="F89" s="4">
         <v>0</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3843,7 +3864,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4073,7 +4094,7 @@
       <c r="F105" s="4">
         <v>0</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G105" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4395,7 +4416,7 @@
       <c r="F119" s="4">
         <v>0</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4441,7 +4462,7 @@
       <c r="F121" s="4">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4760,10 +4781,10 @@
       <c r="E135">
         <v>120</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="6">
         <v>2</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4875,10 +4896,10 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="6">
         <v>3</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4970,7 +4991,7 @@
       <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4990,10 +5011,10 @@
       <c r="E145">
         <v>120</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="6">
         <v>1</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5082,10 +5103,10 @@
       <c r="E149">
         <v>120</v>
       </c>
-      <c r="F149" s="5">
+      <c r="F149" s="6">
         <v>1</v>
       </c>
-      <c r="G149" s="3" t="s">
+      <c r="G149" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5151,10 +5172,10 @@
       <c r="E152">
         <v>120</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152" s="6">
         <v>2</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G152" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5177,7 +5198,7 @@
       <c r="F153" s="4">
         <v>0</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="G153" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5335,10 +5356,10 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160" s="6">
         <v>6</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5568,7 +5589,7 @@
       <c r="F170" s="4">
         <v>0</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5706,7 +5727,7 @@
       <c r="F176" s="4">
         <v>0</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5729,7 +5750,7 @@
       <c r="F177" s="4">
         <v>0</v>
       </c>
-      <c r="G177" s="3" t="s">
+      <c r="G177" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5772,10 +5793,10 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="6">
         <v>1</v>
       </c>
-      <c r="G179" s="3" t="s">
+      <c r="G179" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5798,7 +5819,7 @@
       <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5821,7 +5842,7 @@
       <c r="F181" s="4">
         <v>0</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6002,10 +6023,10 @@
       <c r="E189">
         <v>18</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189" s="6">
         <v>4</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="G189" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6212,7 +6233,7 @@
       <c r="F198" s="4">
         <v>0</v>
       </c>
-      <c r="G198" s="3" t="s">
+      <c r="G198" s="5" t="s">
         <v>21</v>
       </c>
     </row>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="557">
   <si>
     <t>#</t>
   </si>
@@ -61,6 +61,9 @@
     <t>16727</t>
   </si>
   <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
   </si>
   <si>
@@ -82,12 +85,18 @@
     <t>16757</t>
   </si>
   <si>
+    <t>7754807167574</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
   </si>
   <si>
     <t>16760</t>
   </si>
   <si>
+    <t>7754807167604</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
   </si>
   <si>
@@ -100,6 +109,9 @@
     <t>16761</t>
   </si>
   <si>
+    <t>7754807167611</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
   </si>
   <si>
@@ -112,18 +124,27 @@
     <t>16762</t>
   </si>
   <si>
+    <t>7754807167628</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
   </si>
   <si>
     <t>16706</t>
   </si>
   <si>
+    <t>7754807167062</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
   </si>
   <si>
     <t>16708</t>
   </si>
   <si>
+    <t>7754807167086</t>
+  </si>
+  <si>
     <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
   </si>
   <si>
@@ -133,6 +154,9 @@
     <t>14375</t>
   </si>
   <si>
+    <t>7754807143752</t>
+  </si>
+  <si>
     <t>FUTSAL CUERO VULC #3.5</t>
   </si>
   <si>
@@ -229,12 +253,18 @@
     <t>16730</t>
   </si>
   <si>
+    <t>7754807167307</t>
+  </si>
+  <si>
     <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
   </si>
   <si>
     <t>16788</t>
   </si>
   <si>
+    <t>7754807167888</t>
+  </si>
+  <si>
     <t>VOLEY CUERO COSIDO CREW</t>
   </si>
   <si>
@@ -259,138 +289,207 @@
     <t>16004</t>
   </si>
   <si>
+    <t>7754807160049</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA SPARTANO #3</t>
   </si>
   <si>
     <t>15938</t>
   </si>
   <si>
+    <t>7754807159388</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA FREE #5</t>
   </si>
   <si>
     <t>16678</t>
   </si>
   <si>
+    <t>7754807166782</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA URBAN #5</t>
   </si>
   <si>
     <t>16724</t>
   </si>
   <si>
+    <t>7754807167246</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA SPECTRE #5</t>
   </si>
   <si>
     <t>16783</t>
   </si>
   <si>
+    <t>7754807167833</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA INVICTUS  #5</t>
   </si>
   <si>
     <t>14323</t>
   </si>
   <si>
+    <t>7754807143233</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA PAISES BLANCO #5</t>
   </si>
   <si>
     <t>14796</t>
   </si>
   <si>
+    <t>7754807147965</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA TEAM #5</t>
   </si>
   <si>
     <t>11883</t>
   </si>
   <si>
+    <t>7754807118835</t>
+  </si>
+  <si>
     <t>FUTBOL GOMA PAISES COLORES #5</t>
   </si>
   <si>
     <t>16657</t>
   </si>
   <si>
+    <t>7754807166577</t>
+  </si>
+  <si>
     <t>VOLEY GOMA BUTTERFLY</t>
   </si>
   <si>
     <t>15936</t>
   </si>
   <si>
+    <t>7754807159364</t>
+  </si>
+  <si>
     <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
   </si>
   <si>
     <t>14268</t>
   </si>
   <si>
+    <t>7754807142687</t>
+  </si>
+  <si>
     <t>VOLEY VINIBALL GOMA TRICOLOR</t>
   </si>
   <si>
     <t>16784</t>
   </si>
   <si>
+    <t>7754807167840</t>
+  </si>
+  <si>
     <t>VOLEY GOMA FLORES2</t>
   </si>
   <si>
     <t>16786</t>
   </si>
   <si>
+    <t>7754807167864</t>
+  </si>
+  <si>
     <t>VOLEY GOMA FRUTAS2</t>
   </si>
   <si>
     <t>15939</t>
   </si>
   <si>
+    <t>7754807159395</t>
+  </si>
+  <si>
     <t>VOLEY VINIBALL GOMA FOLK</t>
   </si>
   <si>
     <t>16785</t>
   </si>
   <si>
+    <t>7754807167857</t>
+  </si>
+  <si>
     <t>VOLEY GOMA MARIPOSAS</t>
   </si>
   <si>
     <t>16787</t>
   </si>
   <si>
+    <t>7754807167871</t>
+  </si>
+  <si>
     <t>VOLEY GOMA URBANA</t>
   </si>
   <si>
     <t>16672</t>
   </si>
   <si>
+    <t>7754807166720</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #3 SONRISAS</t>
   </si>
   <si>
     <t>14271</t>
   </si>
   <si>
+    <t>7754807142717</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #3 NARANJA</t>
   </si>
   <si>
     <t>14270</t>
   </si>
   <si>
+    <t>7754807111638</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #5 NARANJA</t>
   </si>
   <si>
     <t>14277</t>
   </si>
   <si>
+    <t>7754807142779</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #7 NARANJA</t>
   </si>
   <si>
     <t>15933</t>
   </si>
   <si>
+    <t>7754807159333</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #7 PERU</t>
   </si>
   <si>
     <t>16676</t>
   </si>
   <si>
+    <t>7754807166768</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #5 GALAXY</t>
   </si>
   <si>
     <t>16675</t>
   </si>
   <si>
+    <t>7754807166751</t>
+  </si>
+  <si>
     <t>BASQUET GOMA #7 GALAXY</t>
   </si>
   <si>
@@ -433,18 +532,27 @@
     <t>11603</t>
   </si>
   <si>
+    <t>7754807116039</t>
+  </si>
+  <si>
     <t>N DEPORTIVA FUTBOL PENTA BLANCO #5</t>
   </si>
   <si>
     <t>15945</t>
   </si>
   <si>
+    <t>7754807159456</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA FUTBOL TEAM BRASIL #5</t>
   </si>
   <si>
     <t>15947</t>
   </si>
   <si>
+    <t>7754807159470</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA FUTBOL TEAM ESPAÑA #5</t>
   </si>
   <si>
@@ -457,42 +565,63 @@
     <t>15944</t>
   </si>
   <si>
+    <t>7754807159449</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA FUTBOL TEAM PERU #5</t>
   </si>
   <si>
     <t>15946</t>
   </si>
   <si>
+    <t>7754807159463</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA FUTBOL TEAM ARGENTINA #5</t>
   </si>
   <si>
     <t>15948</t>
   </si>
   <si>
+    <t>7754807159487</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA FUTBOL TEAM ALEMANIA #5</t>
   </si>
   <si>
     <t>11019</t>
   </si>
   <si>
+    <t>7754807110198</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA FUTBOL CRACKCITO BLANCO C/ROJO</t>
   </si>
   <si>
     <t>1240</t>
   </si>
   <si>
+    <t>7754807012409</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA FUTBOL CRACKCITO BL/AZL</t>
   </si>
   <si>
     <t>14741</t>
   </si>
   <si>
+    <t>7754807147415</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA FUTBOL CRACKCITO BICOLOR NEON</t>
   </si>
   <si>
     <t>14384</t>
   </si>
   <si>
+    <t>7754807143844</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA FUTBOL CRACKCITO MULTICOLOR</t>
   </si>
   <si>
@@ -505,24 +634,36 @@
     <t>16715</t>
   </si>
   <si>
+    <t>7754807167154</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA FUTBOL CRACKCITO STELLAR</t>
   </si>
   <si>
     <t>15345</t>
   </si>
   <si>
+    <t>7754807153454</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA FUTBOL CHAMPION</t>
   </si>
   <si>
     <t>15931</t>
   </si>
   <si>
+    <t>7754807159319</t>
+  </si>
+  <si>
     <t>FUTBOL SEMI DEPORTIVA CRACKCITO STAR #5</t>
   </si>
   <si>
     <t>15992</t>
   </si>
   <si>
+    <t>7754807159920</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA CRACKCITO TRAINING</t>
   </si>
   <si>
@@ -541,12 +682,18 @@
     <t>15349</t>
   </si>
   <si>
+    <t>7754807153492</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA FUTBOL SPIDERMAN 01</t>
   </si>
   <si>
     <t>15350</t>
   </si>
   <si>
+    <t>7754807153508</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA FUTBOL SPIDERMAN 02</t>
   </si>
   <si>
@@ -559,108 +706,162 @@
     <t>14733</t>
   </si>
   <si>
+    <t>7754807147330</t>
+  </si>
+  <si>
     <t>N DEPORTIVA VOLEY GABY RAINBOW</t>
   </si>
   <si>
     <t>1706</t>
   </si>
   <si>
+    <t>7754807017060</t>
+  </si>
+  <si>
     <t>N DEPORTIVA VOLEY GABY CALCO BLANCA</t>
   </si>
   <si>
     <t>16718</t>
   </si>
   <si>
+    <t>7754807167185</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA VOLEY GABY TRI MAG-NAR-CEL</t>
   </si>
   <si>
     <t>16719</t>
   </si>
   <si>
+    <t>7754807167192</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA VOLEY GABY TRI LIL-AMA-MAG</t>
   </si>
   <si>
     <t>16720</t>
   </si>
   <si>
+    <t>7754807167208</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA VOLEY GABY TRI VER-AMA-ROJ</t>
   </si>
   <si>
     <t>16721</t>
   </si>
   <si>
+    <t>7754807167215</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC DEPORTIVA VOLEY GABY TRI VER-LIL-ROS</t>
   </si>
   <si>
     <t>1707</t>
   </si>
   <si>
+    <t>7754807017077</t>
+  </si>
+  <si>
     <t>N DEPORTIVA VOLEY GABY TRI BLA-AZL-AMA</t>
   </si>
   <si>
     <t>11028</t>
   </si>
   <si>
+    <t>7754807110280</t>
+  </si>
+  <si>
     <t>N DEPORTIVA VOLEY GABY TRI BLA-AZL-FUC</t>
   </si>
   <si>
     <t>11950</t>
   </si>
   <si>
+    <t>7754807119504</t>
+  </si>
+  <si>
     <t>N DEPORTIVA VOLEY GABY TRI AMA-FUC-CEL</t>
   </si>
   <si>
     <t>14734</t>
   </si>
   <si>
+    <t>7754807147347</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA RAINBOW</t>
   </si>
   <si>
     <t>1709</t>
   </si>
   <si>
+    <t>7754807017091</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA CALCO BLANCA</t>
   </si>
   <si>
     <t>14775</t>
   </si>
   <si>
+    <t>7754807147750</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA SWEET</t>
   </si>
   <si>
     <t>15993</t>
   </si>
   <si>
+    <t>7754807159937</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA CHIBOLITA VOLEY SPRING</t>
   </si>
   <si>
     <t>11262</t>
   </si>
   <si>
+    <t>7754807112628</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA TRI BLA-AZL-AMA</t>
   </si>
   <si>
     <t>11263</t>
   </si>
   <si>
+    <t>7754807112635</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA TRI BLA-AZL-MGT</t>
   </si>
   <si>
     <t>11861</t>
   </si>
   <si>
+    <t>7754807118613</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA TRI AMA-FUC-CEL</t>
   </si>
   <si>
     <t>15287</t>
   </si>
   <si>
+    <t>7754807152877</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY PRINCESAS 01</t>
   </si>
   <si>
     <t>15288</t>
   </si>
   <si>
+    <t>7754807152884</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY PRINCESAS 02</t>
   </si>
   <si>
@@ -673,12 +874,18 @@
     <t>15301</t>
   </si>
   <si>
+    <t>7754807153010</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY SMILES</t>
   </si>
   <si>
     <t>15281</t>
   </si>
   <si>
+    <t>7754807152815</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY ANIMAL PRINT</t>
   </si>
   <si>
@@ -691,6 +898,9 @@
     <t>15290</t>
   </si>
   <si>
+    <t>7754807152907</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY KAWAII 03</t>
   </si>
   <si>
@@ -703,66 +913,99 @@
     <t>12536</t>
   </si>
   <si>
+    <t>7754807125369</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA CHIBOLITA VOLEY FLORES</t>
   </si>
   <si>
     <t>12537</t>
   </si>
   <si>
+    <t>7754807125376</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA CHIBOLITA VOLEY FLORES ROSADA</t>
   </si>
   <si>
     <t>15282</t>
   </si>
   <si>
+    <t>7754807152822</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC SEMIDEPORTIVA VOLEY KAWAII</t>
   </si>
   <si>
     <t>14762</t>
   </si>
   <si>
+    <t>7754807147620</t>
+  </si>
+  <si>
     <t>N SEMIDEPORTIVA VOLEY CHIBOLITA TRENDY</t>
   </si>
   <si>
     <t>11253</t>
   </si>
   <si>
+    <t>7754807112536</t>
+  </si>
+  <si>
     <t>INFLABLE PARA GIMNASIA VINIGYM BALL 65 SPORT</t>
   </si>
   <si>
     <t>11254</t>
   </si>
   <si>
+    <t>7754807112543</t>
+  </si>
+  <si>
     <t>INFLABLE PARA GIMNASIA VINIGYM BALL 75 SPORT</t>
   </si>
   <si>
     <t>14844</t>
   </si>
   <si>
+    <t>7754807148443</t>
+  </si>
+  <si>
     <t>INFLABLE PARA GIMNASIA VINIGYM BALL 65 SPORT SWEET</t>
   </si>
   <si>
     <t>14843</t>
   </si>
   <si>
+    <t>7754807148436</t>
+  </si>
+  <si>
     <t>INFLABLE PARA GIMNASIA VINIGYM BALL 75 SPORT SWEET</t>
   </si>
   <si>
     <t>14410</t>
   </si>
   <si>
+    <t>7754807144100</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC STRESSBALL SWEET FELICES</t>
   </si>
   <si>
     <t>14429</t>
   </si>
   <si>
+    <t>7754807144292</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC STRESSBALL SWEET</t>
   </si>
   <si>
     <t>14649</t>
   </si>
   <si>
+    <t>7754807146494</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC STRESSBALL BE POSITIVE</t>
   </si>
   <si>
@@ -775,6 +1018,9 @@
     <t>11500</t>
   </si>
   <si>
+    <t>7754807115001</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC STRESSBALL CARITAS EXPORTACION</t>
   </si>
   <si>
@@ -787,42 +1033,63 @@
     <t>13888</t>
   </si>
   <si>
+    <t>7754807138888</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC BABY BALL ANIMALITOS</t>
   </si>
   <si>
     <t>12230</t>
   </si>
   <si>
+    <t>7754807122306</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PERFUMADA TUTTI FRUTI</t>
   </si>
   <si>
     <t>14910</t>
   </si>
   <si>
+    <t>7754807149105</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 HAPPY SUMMER</t>
   </si>
   <si>
     <t>14945</t>
   </si>
   <si>
+    <t>7754807149457</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 KAWAII CUTE</t>
   </si>
   <si>
     <t>14949</t>
   </si>
   <si>
+    <t>7754807149495</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 DINO CUTE</t>
   </si>
   <si>
     <t>14467</t>
   </si>
   <si>
+    <t>7754807144674</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 TRENDY GIRL</t>
   </si>
   <si>
     <t>15104</t>
   </si>
   <si>
+    <t>7754807151047</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 ANIMALES CUTE 1</t>
   </si>
   <si>
@@ -835,102 +1102,153 @@
     <t>14899</t>
   </si>
   <si>
+    <t>7754807148993</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 CHILDREN</t>
   </si>
   <si>
     <t>14845</t>
   </si>
   <si>
+    <t>7754807148450</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 DRAGONES</t>
   </si>
   <si>
     <t>14861</t>
   </si>
   <si>
+    <t>7754807148610</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BOYS</t>
   </si>
   <si>
     <t>14946</t>
   </si>
   <si>
+    <t>7754807149464</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 UNICORN CUTE</t>
   </si>
   <si>
     <t>14411</t>
   </si>
   <si>
+    <t>7754807144117</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 ANIMALITOS EN ACCION</t>
   </si>
   <si>
     <t>14829</t>
   </si>
   <si>
+    <t>7754807148290</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 ROBOT</t>
   </si>
   <si>
     <t>15100</t>
   </si>
   <si>
+    <t>7754807151009</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 ANIMALES FANTASTICOS 1</t>
   </si>
   <si>
     <t>15101</t>
   </si>
   <si>
+    <t>7754807151016</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 ANIMALES FANTASTICOS 2</t>
   </si>
   <si>
     <t>15113</t>
   </si>
   <si>
+    <t>7754807151139</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 GATITOS</t>
   </si>
   <si>
     <t>15119</t>
   </si>
   <si>
+    <t>7754807151191</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 AVIONES ROBOT</t>
   </si>
   <si>
     <t>13985</t>
   </si>
   <si>
+    <t>7754807139854</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 MASK</t>
   </si>
   <si>
     <t>13860</t>
   </si>
   <si>
+    <t>7754807138604</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 RAINBOW BOYS</t>
   </si>
   <si>
     <t>13861</t>
   </si>
   <si>
+    <t>7754807138611</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 RAINBOW GIRLS</t>
   </si>
   <si>
     <t>12232</t>
   </si>
   <si>
+    <t>7754807122320</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #7 COLECCION ANIMALES</t>
   </si>
   <si>
     <t>14479</t>
   </si>
   <si>
+    <t>7754807144797</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SPIDERMAN SUBIDA</t>
   </si>
   <si>
     <t>14478</t>
   </si>
   <si>
+    <t>7754807144780</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SPIDERMAN RETRATO</t>
   </si>
   <si>
     <t>14480</t>
   </si>
   <si>
+    <t>7754807144803</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SPIDERMAN THWIP</t>
   </si>
   <si>
@@ -943,126 +1261,189 @@
     <t>15046</t>
   </si>
   <si>
+    <t>7754807150460</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BLUEY 01</t>
   </si>
   <si>
     <t>15048</t>
   </si>
   <si>
+    <t>7754807150484</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BLUEY 03</t>
   </si>
   <si>
     <t>14852</t>
   </si>
   <si>
+    <t>7754807148528</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 FROZEN 2 ANNA</t>
   </si>
   <si>
     <t>14853</t>
   </si>
   <si>
+    <t>7754807148535</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 FROZEN 2 ELSA</t>
   </si>
   <si>
     <t>14854</t>
   </si>
   <si>
+    <t>7754807148542</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 FROZEN 2 HERMANAS</t>
   </si>
   <si>
     <t>14934</t>
   </si>
   <si>
+    <t>7754807149341</t>
+  </si>
+  <si>
     <t>PELOTA ARIEL TYE DIE  #5.5</t>
   </si>
   <si>
     <t>14933</t>
   </si>
   <si>
+    <t>7754807149334</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BLANCA NIEVES TYE DIE</t>
   </si>
   <si>
     <t>14932</t>
   </si>
   <si>
+    <t>7754807149327</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 CENICIENTA TYE DIE</t>
   </si>
   <si>
     <t>14935</t>
   </si>
   <si>
+    <t>7754807149358</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BELLA TYE DIE</t>
   </si>
   <si>
     <t>14929</t>
   </si>
   <si>
+    <t>7754807149297</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 MINNIE TYE DIE</t>
   </si>
   <si>
     <t>14928</t>
   </si>
   <si>
+    <t>7754807149280</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 MICKEY TYE DIE</t>
   </si>
   <si>
     <t>15058</t>
   </si>
   <si>
+    <t>7754807150583</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SONIC 02</t>
   </si>
   <si>
     <t>15060</t>
   </si>
   <si>
+    <t>7754807150606</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SONIC 03</t>
   </si>
   <si>
     <t>15056</t>
   </si>
   <si>
+    <t>7754807150569</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SONIC 01</t>
   </si>
   <si>
     <t>14846</t>
   </si>
   <si>
+    <t>7754807148467</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 AVENGERS HULK PORTRAIT</t>
   </si>
   <si>
     <t>14847</t>
   </si>
   <si>
+    <t>7754807148474</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 AVENGERS IRON MAN PORTRAIT</t>
   </si>
   <si>
     <t>14848</t>
   </si>
   <si>
+    <t>7754807148481</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 AVENGERS CAP AMERICA PORTRAIT</t>
   </si>
   <si>
     <t>15093</t>
   </si>
   <si>
+    <t>7754807150934</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 SPIDEY 01</t>
   </si>
   <si>
     <t>14886</t>
   </si>
   <si>
+    <t>7754807148863</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 LA GRANJA DE ZENON GRUPAL</t>
   </si>
   <si>
     <t>14884</t>
   </si>
   <si>
+    <t>7754807148849</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 BARTOLITO</t>
   </si>
   <si>
     <t>14885</t>
   </si>
   <si>
+    <t>7754807148856</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5.5 LA VACA LOLA</t>
   </si>
   <si>
@@ -1081,36 +1462,54 @@
     <t>15472</t>
   </si>
   <si>
+    <t>7754807154727</t>
+  </si>
+  <si>
     <t>JUGUETE MONTABLE PELOTA SALTARINA LA GRANJA DE ZENON</t>
   </si>
   <si>
     <t>16288</t>
   </si>
   <si>
+    <t>7754807162883</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR KAWAII 02</t>
   </si>
   <si>
     <t>16289</t>
   </si>
   <si>
+    <t>7754807162890</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR KAWAII 03</t>
   </si>
   <si>
     <t>16211</t>
   </si>
   <si>
+    <t>7754807162111</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR UNICORNIO 03</t>
   </si>
   <si>
     <t>16287</t>
   </si>
   <si>
+    <t>7754807162876</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR KAWAII 01</t>
   </si>
   <si>
     <t>16341</t>
   </si>
   <si>
+    <t>7754807163415</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR BLUEY1</t>
   </si>
   <si>
@@ -1123,72 +1522,108 @@
     <t>16227</t>
   </si>
   <si>
+    <t>7754807162272</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR GRANJA BARTOLITO 01</t>
   </si>
   <si>
     <t>16233</t>
   </si>
   <si>
+    <t>7754807162333</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR GRANJA VACA LOLA 01</t>
   </si>
   <si>
     <t>16311</t>
   </si>
   <si>
+    <t>7754807163118</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR MICKEY 01</t>
   </si>
   <si>
     <t>16316</t>
   </si>
   <si>
+    <t>7754807163163</t>
+  </si>
+  <si>
     <t>PELOTA DE PVC RECREATIVA #5 PARA PINTAR MINNIE 01</t>
   </si>
   <si>
     <t>15955</t>
   </si>
   <si>
+    <t>7754807159555</t>
+  </si>
+  <si>
     <t>PELOTA CON PUAS PARA MASCOTAS GRANDES #2</t>
   </si>
   <si>
     <t>15954</t>
   </si>
   <si>
+    <t>7754807159548</t>
+  </si>
+  <si>
     <t>PELOTA CON PUAS PARA MASCOTAS PEQUEÑAS #1</t>
   </si>
   <si>
     <t>16681</t>
   </si>
   <si>
+    <t>7754807166812</t>
+  </si>
+  <si>
     <t>PELOTA CON PUAS PARA MASCOTAS PEQUEÑAS #1 SWEET</t>
   </si>
   <si>
     <t>16682</t>
   </si>
   <si>
+    <t>7754807166829</t>
+  </si>
+  <si>
     <t>PELOTA CON PUAS PARA MASCOTAS GRANDES #2 SWEET</t>
   </si>
   <si>
     <t>MA001</t>
   </si>
   <si>
+    <t>7754807005753</t>
+  </si>
+  <si>
     <t>JUGUETE PARA MASCOTA HUESITO PEQUEÑO NEON</t>
   </si>
   <si>
     <t>MA002</t>
   </si>
   <si>
+    <t>7754807005760</t>
+  </si>
+  <si>
     <t>JUGUETE PARA MASCOTA HUESITO GRANDE NEON</t>
   </si>
   <si>
     <t>MA003</t>
   </si>
   <si>
+    <t>7754807005777</t>
+  </si>
+  <si>
     <t>JUGUETE PARA MASCOTA HUESITO PEQUEÑO PASTEL</t>
   </si>
   <si>
     <t>MA004</t>
   </si>
   <si>
+    <t>7754807005784</t>
+  </si>
+  <si>
     <t>JUGUETE PARA MASCOTA HUESITO GRANDE PASTEL</t>
   </si>
   <si>
@@ -1207,28 +1642,43 @@
     <t>16777</t>
   </si>
   <si>
+    <t>7754807009980</t>
+  </si>
+  <si>
     <t>PELOTA PUAS 1 VINIBALL 12 UN POR EMPAQUE</t>
   </si>
   <si>
     <t>16778</t>
   </si>
   <si>
+    <t>7754807009997</t>
+  </si>
+  <si>
     <t>PELOTA PUAS 2 VINIBALL 12 UN POR EMPAQUE</t>
   </si>
   <si>
     <t>16779</t>
   </si>
   <si>
+    <t>7754807010009</t>
+  </si>
+  <si>
     <t>PELOTA PUAS 3 VINIBALL 12 UN POR EMPAQUE</t>
   </si>
   <si>
     <t>16780</t>
   </si>
   <si>
+    <t>7754807010108</t>
+  </si>
+  <si>
     <t>PELOTA FULL PRINT 1 VINIBALL 12 UN POR EMPAQUE</t>
   </si>
   <si>
     <t>16781</t>
+  </si>
+  <si>
+    <t>7754807010115</t>
   </si>
   <si>
     <t>PELOTA FULL PRINT 2 VINIBALL 12 UN POR EMPAQUE</t>
@@ -1783,10 +2233,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>24</v>
@@ -1803,13 +2253,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -1826,13 +2276,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -1841,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1849,13 +2299,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>24</v>
@@ -1872,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>24</v>
@@ -1895,13 +2345,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>24</v>
@@ -1918,13 +2368,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>24</v>
@@ -1941,13 +2391,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>24</v>
@@ -1964,13 +2414,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>24</v>
@@ -1987,13 +2437,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>36</v>
@@ -2010,13 +2460,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2025,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2033,13 +2483,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
@@ -2056,13 +2506,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>24</v>
@@ -2079,13 +2529,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>36</v>
@@ -2094,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2102,13 +2552,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E19">
         <v>36</v>
@@ -2125,13 +2575,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>36</v>
@@ -2148,13 +2598,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E21">
         <v>36</v>
@@ -2171,13 +2621,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E22">
         <v>36</v>
@@ -2194,13 +2644,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E23">
         <v>48</v>
@@ -2209,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2217,13 +2667,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>48</v>
@@ -2232,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2240,13 +2690,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E25">
         <v>48</v>
@@ -2255,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2263,13 +2713,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>48</v>
@@ -2278,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,13 +2736,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>36</v>
@@ -2301,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2309,13 +2759,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E28">
         <v>36</v>
@@ -2324,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2332,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E29">
         <v>50</v>
@@ -2355,13 +2805,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E30">
         <v>50</v>
@@ -2370,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2378,13 +2828,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>50</v>
@@ -2393,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2401,13 +2851,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
@@ -2424,13 +2874,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
@@ -2447,13 +2897,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>50</v>
@@ -2470,13 +2920,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>50</v>
@@ -2493,13 +2943,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E36">
         <v>50</v>
@@ -2516,13 +2966,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
@@ -2539,13 +2989,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
@@ -2562,13 +3012,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
@@ -2577,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2585,13 +3035,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
@@ -2600,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,13 +3058,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
@@ -2623,7 +3073,7 @@
         <v>5</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2631,13 +3081,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
@@ -2654,13 +3104,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
@@ -2669,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2677,13 +3127,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
@@ -2700,13 +3150,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
@@ -2715,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2723,13 +3173,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
@@ -2738,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2746,13 +3196,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
@@ -2769,13 +3219,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
@@ -2784,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2792,13 +3242,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2807,7 +3257,7 @@
         <v>6</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2815,13 +3265,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
@@ -2838,13 +3288,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
@@ -2853,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2861,13 +3311,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
@@ -2884,13 +3334,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
@@ -2899,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2907,13 +3357,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
@@ -2930,13 +3380,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
@@ -2953,13 +3403,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
@@ -2976,13 +3426,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
@@ -2999,13 +3449,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
@@ -3014,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3022,13 +3472,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
@@ -3037,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3045,13 +3495,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="E60">
         <v>36</v>
@@ -3068,13 +3518,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="E61">
         <v>36</v>
@@ -3083,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3091,13 +3541,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="E62">
         <v>36</v>
@@ -3114,13 +3564,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="E63">
         <v>36</v>
@@ -3137,13 +3587,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>48</v>
@@ -3160,13 +3610,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s">
         <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="E65">
         <v>48</v>
@@ -3183,13 +3633,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="D66" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="E66">
         <v>60</v>
@@ -3206,13 +3656,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="E67">
         <v>60</v>
@@ -3229,13 +3679,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="E68">
         <v>60</v>
@@ -3252,13 +3702,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="E69">
         <v>60</v>
@@ -3275,13 +3725,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="E70">
         <v>60</v>
@@ -3298,13 +3748,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="E71">
         <v>60</v>
@@ -3321,13 +3771,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="D72" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="E72">
         <v>60</v>
@@ -3336,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3344,13 +3794,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>193</v>
       </c>
       <c r="D73" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="E73">
         <v>60</v>
@@ -3367,13 +3817,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E74">
         <v>60</v>
@@ -3390,13 +3840,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="E75">
         <v>60</v>
@@ -3413,13 +3863,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="D76" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="E76">
         <v>60</v>
@@ -3436,13 +3886,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
         <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="E77">
         <v>60</v>
@@ -3459,13 +3909,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="D78" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="E78">
         <v>60</v>
@@ -3482,13 +3932,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="D79" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="E79">
         <v>60</v>
@@ -3505,13 +3955,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>213</v>
       </c>
       <c r="D80" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="E80">
         <v>60</v>
@@ -3528,13 +3978,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>216</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="E81">
         <v>60</v>
@@ -3543,7 +3993,7 @@
         <v>5</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3551,13 +4001,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="E82">
         <v>60</v>
@@ -3574,13 +4024,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="E83">
         <v>60</v>
@@ -3597,13 +4047,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>223</v>
       </c>
       <c r="D84" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="E84">
         <v>60</v>
@@ -3612,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3620,13 +4070,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="D85" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="E85">
         <v>60</v>
@@ -3643,13 +4093,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="C86" t="s">
         <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="E86">
         <v>60</v>
@@ -3666,13 +4116,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>231</v>
       </c>
       <c r="D87" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="E87">
         <v>60</v>
@@ -3689,13 +4139,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="D88" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="E88">
         <v>60</v>
@@ -3704,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -3712,13 +4162,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>237</v>
       </c>
       <c r="D89" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="E89">
         <v>60</v>
@@ -3727,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -3735,13 +4185,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="D90" t="s">
-        <v>188</v>
+        <v>241</v>
       </c>
       <c r="E90">
         <v>60</v>
@@ -3758,13 +4208,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>243</v>
       </c>
       <c r="D91" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="E91">
         <v>60</v>
@@ -3781,13 +4231,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>246</v>
       </c>
       <c r="D92" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="E92">
         <v>60</v>
@@ -3804,13 +4254,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>249</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="E93">
         <v>60</v>
@@ -3827,13 +4277,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="E94">
         <v>60</v>
@@ -3850,13 +4300,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>255</v>
       </c>
       <c r="D95" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="E95">
         <v>60</v>
@@ -3865,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -3873,13 +4323,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>257</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>258</v>
       </c>
       <c r="D96" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="E96">
         <v>60</v>
@@ -3896,13 +4346,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>261</v>
       </c>
       <c r="D97" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="E97">
         <v>60</v>
@@ -3919,13 +4369,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="E98">
         <v>60</v>
@@ -3942,13 +4392,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="E99">
         <v>60</v>
@@ -3965,13 +4415,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="D100" t="s">
-        <v>208</v>
+        <v>271</v>
       </c>
       <c r="E100">
         <v>60</v>
@@ -3988,13 +4438,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>272</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>273</v>
       </c>
       <c r="D101" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="E101">
         <v>60</v>
@@ -4011,13 +4461,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="C102" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="E102">
         <v>60</v>
@@ -4034,13 +4484,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="C103" t="s">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="D103" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="E103">
         <v>60</v>
@@ -4057,13 +4507,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="C104" t="s">
-        <v>8</v>
+        <v>282</v>
       </c>
       <c r="D104" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="E104">
         <v>60</v>
@@ -4080,13 +4530,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E105">
         <v>60</v>
@@ -4095,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4103,13 +4553,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="D106" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="E106">
         <v>60</v>
@@ -4126,13 +4576,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="D107" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="E107">
         <v>60</v>
@@ -4149,13 +4599,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="C108" t="s">
         <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="E108">
         <v>60</v>
@@ -4172,13 +4622,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="D109" t="s">
-        <v>226</v>
+        <v>296</v>
       </c>
       <c r="E109">
         <v>60</v>
@@ -4195,13 +4645,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="C110" t="s">
         <v>8</v>
       </c>
       <c r="D110" t="s">
-        <v>228</v>
+        <v>298</v>
       </c>
       <c r="E110">
         <v>60</v>
@@ -4218,13 +4668,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="C111" t="s">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="D111" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="E111">
         <v>60</v>
@@ -4241,13 +4691,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>231</v>
+        <v>302</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="D112" t="s">
-        <v>232</v>
+        <v>304</v>
       </c>
       <c r="E112">
         <v>60</v>
@@ -4264,13 +4714,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>305</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D113" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="E113">
         <v>60</v>
@@ -4287,13 +4737,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>235</v>
+        <v>308</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="D114" t="s">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="E114">
         <v>60</v>
@@ -4310,13 +4760,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="C115" t="s">
-        <v>8</v>
+        <v>312</v>
       </c>
       <c r="D115" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -4333,13 +4783,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>314</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="D116" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -4356,13 +4806,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>318</v>
       </c>
       <c r="D117" t="s">
-        <v>242</v>
+        <v>319</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -4379,13 +4829,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>243</v>
+        <v>320</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="D118" t="s">
-        <v>244</v>
+        <v>322</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -4402,13 +4852,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>324</v>
       </c>
       <c r="D119" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
       <c r="E119">
         <v>12</v>
@@ -4417,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4425,13 +4875,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>327</v>
       </c>
       <c r="D120" t="s">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="E120">
         <v>36</v>
@@ -4448,13 +4898,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>249</v>
+        <v>329</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="D121" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="E121">
         <v>36</v>
@@ -4463,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4471,13 +4921,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="C122" t="s">
         <v>8</v>
       </c>
       <c r="D122" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="E122">
         <v>12</v>
@@ -4494,13 +4944,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="C123" t="s">
-        <v>8</v>
+        <v>335</v>
       </c>
       <c r="D123" t="s">
-        <v>254</v>
+        <v>336</v>
       </c>
       <c r="E123">
         <v>36</v>
@@ -4517,13 +4967,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>337</v>
       </c>
       <c r="C124" t="s">
         <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>256</v>
+        <v>338</v>
       </c>
       <c r="E124">
         <v>12</v>
@@ -4540,13 +4990,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>257</v>
+        <v>339</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D125" t="s">
-        <v>258</v>
+        <v>341</v>
       </c>
       <c r="E125">
         <v>36</v>
@@ -4563,13 +5013,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>343</v>
       </c>
       <c r="D126" t="s">
-        <v>260</v>
+        <v>344</v>
       </c>
       <c r="E126">
         <v>120</v>
@@ -4586,13 +5036,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="C127" t="s">
-        <v>8</v>
+        <v>346</v>
       </c>
       <c r="D127" t="s">
-        <v>262</v>
+        <v>347</v>
       </c>
       <c r="E127">
         <v>120</v>
@@ -4609,13 +5059,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C128" t="s">
-        <v>8</v>
+        <v>349</v>
       </c>
       <c r="D128" t="s">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="E128">
         <v>120</v>
@@ -4632,13 +5082,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="D129" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="E129">
         <v>120</v>
@@ -4655,13 +5105,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>267</v>
+        <v>354</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>355</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
       <c r="E130">
         <v>120</v>
@@ -4678,13 +5128,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="D131" t="s">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="E131">
         <v>120</v>
@@ -4701,13 +5151,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>271</v>
+        <v>360</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
       </c>
       <c r="D132" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="E132">
         <v>120</v>
@@ -4724,13 +5174,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>363</v>
       </c>
       <c r="D133" t="s">
-        <v>274</v>
+        <v>364</v>
       </c>
       <c r="E133">
         <v>120</v>
@@ -4747,13 +5197,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>366</v>
       </c>
       <c r="D134" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="E134">
         <v>120</v>
@@ -4770,13 +5220,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>368</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>369</v>
       </c>
       <c r="D135" t="s">
-        <v>278</v>
+        <v>370</v>
       </c>
       <c r="E135">
         <v>120</v>
@@ -4785,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -4793,13 +5243,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>372</v>
       </c>
       <c r="D136" t="s">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="E136">
         <v>120</v>
@@ -4816,13 +5266,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>281</v>
+        <v>374</v>
       </c>
       <c r="C137" t="s">
-        <v>8</v>
+        <v>375</v>
       </c>
       <c r="D137" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="E137">
         <v>120</v>
@@ -4839,13 +5289,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>283</v>
+        <v>377</v>
       </c>
       <c r="C138" t="s">
-        <v>8</v>
+        <v>378</v>
       </c>
       <c r="D138" t="s">
-        <v>284</v>
+        <v>379</v>
       </c>
       <c r="E138">
         <v>120</v>
@@ -4862,13 +5312,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>285</v>
+        <v>380</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>381</v>
       </c>
       <c r="D139" t="s">
-        <v>286</v>
+        <v>382</v>
       </c>
       <c r="E139">
         <v>120</v>
@@ -4885,13 +5335,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>287</v>
+        <v>383</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>384</v>
       </c>
       <c r="D140" t="s">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="E140">
         <v>120</v>
@@ -4900,7 +5350,7 @@
         <v>3</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -4908,13 +5358,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>387</v>
       </c>
       <c r="D141" t="s">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="E141">
         <v>120</v>
@@ -4931,13 +5381,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="C142" t="s">
-        <v>8</v>
+        <v>390</v>
       </c>
       <c r="D142" t="s">
-        <v>292</v>
+        <v>391</v>
       </c>
       <c r="E142">
         <v>120</v>
@@ -4954,13 +5404,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C143" t="s">
-        <v>8</v>
+        <v>393</v>
       </c>
       <c r="D143" t="s">
-        <v>294</v>
+        <v>394</v>
       </c>
       <c r="E143">
         <v>120</v>
@@ -4977,13 +5427,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
-        <v>8</v>
+        <v>396</v>
       </c>
       <c r="D144" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
       <c r="E144">
         <v>120</v>
@@ -4992,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5000,13 +5450,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>297</v>
+        <v>398</v>
       </c>
       <c r="C145" t="s">
-        <v>8</v>
+        <v>399</v>
       </c>
       <c r="D145" t="s">
-        <v>298</v>
+        <v>400</v>
       </c>
       <c r="E145">
         <v>120</v>
@@ -5015,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5023,13 +5473,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="C146" t="s">
-        <v>8</v>
+        <v>402</v>
       </c>
       <c r="D146" t="s">
-        <v>300</v>
+        <v>403</v>
       </c>
       <c r="E146">
         <v>60</v>
@@ -5046,13 +5496,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="C147" t="s">
-        <v>8</v>
+        <v>405</v>
       </c>
       <c r="D147" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="E147">
         <v>120</v>
@@ -5069,13 +5519,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>407</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>408</v>
       </c>
       <c r="D148" t="s">
-        <v>304</v>
+        <v>409</v>
       </c>
       <c r="E148">
         <v>120</v>
@@ -5092,13 +5542,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>305</v>
+        <v>410</v>
       </c>
       <c r="C149" t="s">
-        <v>8</v>
+        <v>411</v>
       </c>
       <c r="D149" t="s">
-        <v>306</v>
+        <v>412</v>
       </c>
       <c r="E149">
         <v>120</v>
@@ -5107,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5115,13 +5565,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>307</v>
+        <v>413</v>
       </c>
       <c r="C150" t="s">
         <v>8</v>
       </c>
       <c r="D150" t="s">
-        <v>308</v>
+        <v>414</v>
       </c>
       <c r="E150">
         <v>120</v>
@@ -5138,13 +5588,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>309</v>
+        <v>415</v>
       </c>
       <c r="C151" t="s">
-        <v>8</v>
+        <v>416</v>
       </c>
       <c r="D151" t="s">
-        <v>310</v>
+        <v>417</v>
       </c>
       <c r="E151">
         <v>120</v>
@@ -5161,13 +5611,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="C152" t="s">
-        <v>8</v>
+        <v>419</v>
       </c>
       <c r="D152" t="s">
-        <v>312</v>
+        <v>420</v>
       </c>
       <c r="E152">
         <v>120</v>
@@ -5176,7 +5626,7 @@
         <v>2</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5184,13 +5634,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>313</v>
+        <v>421</v>
       </c>
       <c r="C153" t="s">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="D153" t="s">
-        <v>314</v>
+        <v>423</v>
       </c>
       <c r="E153">
         <v>120</v>
@@ -5199,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5207,13 +5657,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="C154" t="s">
-        <v>8</v>
+        <v>425</v>
       </c>
       <c r="D154" t="s">
-        <v>316</v>
+        <v>426</v>
       </c>
       <c r="E154">
         <v>120</v>
@@ -5230,13 +5680,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>317</v>
+        <v>427</v>
       </c>
       <c r="C155" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D155" t="s">
-        <v>318</v>
+        <v>429</v>
       </c>
       <c r="E155">
         <v>120</v>
@@ -5253,13 +5703,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
-        <v>8</v>
+        <v>431</v>
       </c>
       <c r="D156" t="s">
-        <v>320</v>
+        <v>432</v>
       </c>
       <c r="E156">
         <v>120</v>
@@ -5276,13 +5726,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>321</v>
+        <v>433</v>
       </c>
       <c r="C157" t="s">
-        <v>8</v>
+        <v>434</v>
       </c>
       <c r="D157" t="s">
-        <v>322</v>
+        <v>435</v>
       </c>
       <c r="E157">
         <v>120</v>
@@ -5299,13 +5749,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>323</v>
+        <v>436</v>
       </c>
       <c r="C158" t="s">
-        <v>8</v>
+        <v>437</v>
       </c>
       <c r="D158" t="s">
-        <v>324</v>
+        <v>438</v>
       </c>
       <c r="E158">
         <v>120</v>
@@ -5322,13 +5772,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
       <c r="C159" t="s">
-        <v>8</v>
+        <v>440</v>
       </c>
       <c r="D159" t="s">
-        <v>326</v>
+        <v>441</v>
       </c>
       <c r="E159">
         <v>120</v>
@@ -5345,13 +5795,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>327</v>
+        <v>442</v>
       </c>
       <c r="C160" t="s">
-        <v>8</v>
+        <v>443</v>
       </c>
       <c r="D160" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="E160">
         <v>120</v>
@@ -5360,7 +5810,7 @@
         <v>6</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5368,13 +5818,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>445</v>
       </c>
       <c r="C161" t="s">
-        <v>8</v>
+        <v>446</v>
       </c>
       <c r="D161" t="s">
-        <v>330</v>
+        <v>447</v>
       </c>
       <c r="E161">
         <v>120</v>
@@ -5391,13 +5841,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>448</v>
       </c>
       <c r="C162" t="s">
-        <v>8</v>
+        <v>449</v>
       </c>
       <c r="D162" t="s">
-        <v>332</v>
+        <v>450</v>
       </c>
       <c r="E162">
         <v>120</v>
@@ -5414,13 +5864,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>333</v>
+        <v>451</v>
       </c>
       <c r="C163" t="s">
-        <v>8</v>
+        <v>452</v>
       </c>
       <c r="D163" t="s">
-        <v>334</v>
+        <v>453</v>
       </c>
       <c r="E163">
         <v>120</v>
@@ -5437,13 +5887,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>454</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>455</v>
       </c>
       <c r="D164" t="s">
-        <v>336</v>
+        <v>456</v>
       </c>
       <c r="E164">
         <v>120</v>
@@ -5460,13 +5910,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>337</v>
+        <v>457</v>
       </c>
       <c r="C165" t="s">
-        <v>8</v>
+        <v>458</v>
       </c>
       <c r="D165" t="s">
-        <v>338</v>
+        <v>459</v>
       </c>
       <c r="E165">
         <v>120</v>
@@ -5483,13 +5933,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>339</v>
+        <v>460</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>461</v>
       </c>
       <c r="D166" t="s">
-        <v>340</v>
+        <v>462</v>
       </c>
       <c r="E166">
         <v>120</v>
@@ -5506,13 +5956,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
+        <v>463</v>
       </c>
       <c r="C167" t="s">
-        <v>8</v>
+        <v>464</v>
       </c>
       <c r="D167" t="s">
-        <v>342</v>
+        <v>465</v>
       </c>
       <c r="E167">
         <v>120</v>
@@ -5529,13 +5979,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>343</v>
+        <v>466</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>467</v>
       </c>
       <c r="D168" t="s">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="E168">
         <v>120</v>
@@ -5552,13 +6002,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="C169" t="s">
-        <v>8</v>
+        <v>470</v>
       </c>
       <c r="D169" t="s">
-        <v>346</v>
+        <v>471</v>
       </c>
       <c r="E169">
         <v>120</v>
@@ -5575,13 +6025,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>472</v>
       </c>
       <c r="C170" t="s">
-        <v>8</v>
+        <v>473</v>
       </c>
       <c r="D170" t="s">
-        <v>348</v>
+        <v>474</v>
       </c>
       <c r="E170">
         <v>120</v>
@@ -5590,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5598,13 +6048,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>349</v>
+        <v>475</v>
       </c>
       <c r="C171" t="s">
-        <v>8</v>
+        <v>476</v>
       </c>
       <c r="D171" t="s">
-        <v>350</v>
+        <v>477</v>
       </c>
       <c r="E171">
         <v>120</v>
@@ -5621,13 +6071,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>351</v>
+        <v>478</v>
       </c>
       <c r="C172" t="s">
         <v>8</v>
       </c>
       <c r="D172" t="s">
-        <v>352</v>
+        <v>479</v>
       </c>
       <c r="E172">
         <v>120</v>
@@ -5644,13 +6094,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>353</v>
+        <v>480</v>
       </c>
       <c r="C173" t="s">
         <v>8</v>
       </c>
       <c r="D173" t="s">
-        <v>354</v>
+        <v>481</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -5667,13 +6117,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>355</v>
+        <v>482</v>
       </c>
       <c r="C174" t="s">
-        <v>8</v>
+        <v>483</v>
       </c>
       <c r="D174" t="s">
-        <v>356</v>
+        <v>484</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -5690,13 +6140,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>485</v>
       </c>
       <c r="C175" t="s">
-        <v>8</v>
+        <v>486</v>
       </c>
       <c r="D175" t="s">
-        <v>358</v>
+        <v>487</v>
       </c>
       <c r="E175">
         <v>12</v>
@@ -5713,13 +6163,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="C176" t="s">
-        <v>8</v>
+        <v>489</v>
       </c>
       <c r="D176" t="s">
-        <v>360</v>
+        <v>490</v>
       </c>
       <c r="E176">
         <v>12</v>
@@ -5728,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -5736,13 +6186,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>361</v>
+        <v>491</v>
       </c>
       <c r="C177" t="s">
-        <v>8</v>
+        <v>492</v>
       </c>
       <c r="D177" t="s">
-        <v>362</v>
+        <v>493</v>
       </c>
       <c r="E177">
         <v>12</v>
@@ -5751,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -5759,13 +6209,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>363</v>
+        <v>494</v>
       </c>
       <c r="C178" t="s">
-        <v>8</v>
+        <v>495</v>
       </c>
       <c r="D178" t="s">
-        <v>364</v>
+        <v>496</v>
       </c>
       <c r="E178">
         <v>12</v>
@@ -5782,13 +6232,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>365</v>
+        <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>498</v>
       </c>
       <c r="D179" t="s">
-        <v>366</v>
+        <v>499</v>
       </c>
       <c r="E179">
         <v>12</v>
@@ -5797,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -5805,13 +6255,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>367</v>
+        <v>500</v>
       </c>
       <c r="C180" t="s">
         <v>8</v>
       </c>
       <c r="D180" t="s">
-        <v>368</v>
+        <v>501</v>
       </c>
       <c r="E180">
         <v>12</v>
@@ -5820,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -5828,13 +6278,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>369</v>
+        <v>502</v>
       </c>
       <c r="C181" t="s">
-        <v>8</v>
+        <v>503</v>
       </c>
       <c r="D181" t="s">
-        <v>370</v>
+        <v>504</v>
       </c>
       <c r="E181">
         <v>12</v>
@@ -5843,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -5851,13 +6301,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>371</v>
+        <v>505</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>506</v>
       </c>
       <c r="D182" t="s">
-        <v>372</v>
+        <v>507</v>
       </c>
       <c r="E182">
         <v>12</v>
@@ -5874,13 +6324,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>373</v>
+        <v>508</v>
       </c>
       <c r="C183" t="s">
-        <v>8</v>
+        <v>509</v>
       </c>
       <c r="D183" t="s">
-        <v>374</v>
+        <v>510</v>
       </c>
       <c r="E183">
         <v>12</v>
@@ -5897,13 +6347,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>375</v>
+        <v>511</v>
       </c>
       <c r="C184" t="s">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="D184" t="s">
-        <v>376</v>
+        <v>513</v>
       </c>
       <c r="E184">
         <v>12</v>
@@ -5920,13 +6370,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>377</v>
+        <v>514</v>
       </c>
       <c r="C185" t="s">
-        <v>8</v>
+        <v>515</v>
       </c>
       <c r="D185" t="s">
-        <v>378</v>
+        <v>516</v>
       </c>
       <c r="E185">
         <v>12</v>
@@ -5943,13 +6393,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>379</v>
+        <v>517</v>
       </c>
       <c r="C186" t="s">
-        <v>8</v>
+        <v>518</v>
       </c>
       <c r="D186" t="s">
-        <v>380</v>
+        <v>519</v>
       </c>
       <c r="E186">
         <v>12</v>
@@ -5966,13 +6416,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>381</v>
+        <v>520</v>
       </c>
       <c r="C187" t="s">
-        <v>8</v>
+        <v>521</v>
       </c>
       <c r="D187" t="s">
-        <v>382</v>
+        <v>522</v>
       </c>
       <c r="E187">
         <v>12</v>
@@ -5989,13 +6439,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>383</v>
+        <v>523</v>
       </c>
       <c r="C188" t="s">
-        <v>8</v>
+        <v>524</v>
       </c>
       <c r="D188" t="s">
-        <v>384</v>
+        <v>525</v>
       </c>
       <c r="E188">
         <v>12</v>
@@ -6012,13 +6462,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>385</v>
+        <v>526</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>527</v>
       </c>
       <c r="D189" t="s">
-        <v>386</v>
+        <v>528</v>
       </c>
       <c r="E189">
         <v>18</v>
@@ -6027,7 +6477,7 @@
         <v>4</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6035,13 +6485,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>387</v>
+        <v>529</v>
       </c>
       <c r="C190" t="s">
-        <v>8</v>
+        <v>530</v>
       </c>
       <c r="D190" t="s">
-        <v>388</v>
+        <v>531</v>
       </c>
       <c r="E190">
         <v>12</v>
@@ -6058,13 +6508,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>389</v>
+        <v>532</v>
       </c>
       <c r="C191" t="s">
-        <v>8</v>
+        <v>533</v>
       </c>
       <c r="D191" t="s">
-        <v>390</v>
+        <v>534</v>
       </c>
       <c r="E191">
         <v>18</v>
@@ -6081,13 +6531,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>391</v>
+        <v>535</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>536</v>
       </c>
       <c r="D192" t="s">
-        <v>392</v>
+        <v>537</v>
       </c>
       <c r="E192">
         <v>12</v>
@@ -6104,13 +6554,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>393</v>
+        <v>538</v>
       </c>
       <c r="C193" t="s">
         <v>8</v>
       </c>
       <c r="D193" t="s">
-        <v>394</v>
+        <v>539</v>
       </c>
       <c r="E193">
         <v>400</v>
@@ -6127,13 +6577,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>395</v>
+        <v>540</v>
       </c>
       <c r="C194" t="s">
         <v>8</v>
       </c>
       <c r="D194" t="s">
-        <v>396</v>
+        <v>541</v>
       </c>
       <c r="E194">
         <v>400</v>
@@ -6150,13 +6600,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>397</v>
+        <v>542</v>
       </c>
       <c r="C195" t="s">
-        <v>8</v>
+        <v>543</v>
       </c>
       <c r="D195" t="s">
-        <v>398</v>
+        <v>544</v>
       </c>
       <c r="E195">
         <v>120</v>
@@ -6173,13 +6623,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>399</v>
+        <v>545</v>
       </c>
       <c r="C196" t="s">
-        <v>8</v>
+        <v>546</v>
       </c>
       <c r="D196" t="s">
-        <v>400</v>
+        <v>547</v>
       </c>
       <c r="E196">
         <v>120</v>
@@ -6196,13 +6646,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>401</v>
+        <v>548</v>
       </c>
       <c r="C197" t="s">
-        <v>8</v>
+        <v>549</v>
       </c>
       <c r="D197" t="s">
-        <v>402</v>
+        <v>550</v>
       </c>
       <c r="E197">
         <v>120</v>
@@ -6219,13 +6669,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>403</v>
+        <v>551</v>
       </c>
       <c r="C198" t="s">
-        <v>8</v>
+        <v>552</v>
       </c>
       <c r="D198" t="s">
-        <v>404</v>
+        <v>553</v>
       </c>
       <c r="E198">
         <v>120</v>
@@ -6234,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6242,13 +6692,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>405</v>
+        <v>554</v>
       </c>
       <c r="C199" t="s">
-        <v>8</v>
+        <v>555</v>
       </c>
       <c r="D199" t="s">
-        <v>406</v>
+        <v>556</v>
       </c>
       <c r="E199">
         <v>120</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -2379,11 +2379,11 @@
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>180</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>15</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2425,11 +2425,11 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>168</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>15</v>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2448,11 +2448,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>182</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>15</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2908,11 +2908,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>263</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>15</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3414,11 +3414,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>196</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>15</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3598,11 +3598,11 @@
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>418</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>15</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4104,11 +4104,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>333</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>15</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4518,11 +4518,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>368</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>15</v>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4886,11 +4886,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>261</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>15</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5093,11 +5093,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>1067</v>
       </c>
-      <c r="G129" s="5" t="s">
-        <v>15</v>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5116,11 +5116,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>884</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>15</v>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5208,11 +5208,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>1017</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>15</v>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5691,11 +5691,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>908</v>
       </c>
-      <c r="G155" s="5" t="s">
-        <v>15</v>
+      <c r="G155" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5760,11 +5760,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="4">
+      <c r="F158" s="2">
         <v>1101</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>15</v>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5967,11 +5967,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="4">
+      <c r="F167" s="2">
         <v>764</v>
       </c>
-      <c r="G167" s="5" t="s">
-        <v>15</v>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -6013,11 +6013,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="4">
+      <c r="F169" s="2">
         <v>703</v>
       </c>
-      <c r="G169" s="5" t="s">
-        <v>15</v>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -52,475 +52,475 @@
     <t>FUTBOL CUERO TERMOSELLADA PRECISION #5</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
     <t>016726</t>
   </si>
   <si>
     <t>FUTBOL CUERO TERMOSELLADA DUPLO #5</t>
   </si>
   <si>
+    <t>016727</t>
+  </si>
+  <si>
+    <t>7754807167277</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
+  </si>
+  <si>
+    <t>016756</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
+  </si>
+  <si>
+    <t>016755</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
+  </si>
+  <si>
+    <t>016757</t>
+  </si>
+  <si>
+    <t>7754807167574</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
+  </si>
+  <si>
+    <t>016760</t>
+  </si>
+  <si>
+    <t>7754807167604</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
+  </si>
+  <si>
+    <t>016758</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
+  </si>
+  <si>
+    <t>016761</t>
+  </si>
+  <si>
+    <t>7754807167611</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
+  </si>
+  <si>
+    <t>016759</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
+  </si>
+  <si>
+    <t>016762</t>
+  </si>
+  <si>
+    <t>7754807167628</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
+  </si>
+  <si>
+    <t>016706</t>
+  </si>
+  <si>
+    <t>7754807167062</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
+  </si>
+  <si>
+    <t>016708</t>
+  </si>
+  <si>
+    <t>7754807167086</t>
+  </si>
+  <si>
+    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
+  </si>
+  <si>
+    <t>014375</t>
+  </si>
+  <si>
+    <t>7754807143752</t>
+  </si>
+  <si>
+    <t>FUTSAL CUERO VULC #3.5</t>
+  </si>
+  <si>
+    <t>016766</t>
+  </si>
+  <si>
+    <t>FUTSAL TERMOSELLADA ALEGRO</t>
+  </si>
+  <si>
+    <t>016767</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
+  </si>
+  <si>
+    <t>016768</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
+  </si>
+  <si>
+    <t>016769</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
+  </si>
+  <si>
+    <t>016770</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
+  </si>
+  <si>
+    <t>016771</t>
+  </si>
+  <si>
+    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
+  </si>
+  <si>
+    <t>016743</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU PER2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016744</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU BRA2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016745</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU ARG2 CUP24 #5</t>
+  </si>
+  <si>
+    <t>016746</t>
+  </si>
+  <si>
+    <t>FUTBOL TPU FLAGS CUP24 #5</t>
+  </si>
+  <si>
+    <t>016747</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA1</t>
+  </si>
+  <si>
+    <t>016748</t>
+  </si>
+  <si>
+    <t>VOLEY PU LIGA2</t>
+  </si>
+  <si>
+    <t>016729</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FLORES</t>
+  </si>
+  <si>
+    <t>016731</t>
+  </si>
+  <si>
+    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
+  </si>
+  <si>
+    <t>016728</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK</t>
+  </si>
+  <si>
+    <t>016730</t>
+  </si>
+  <si>
+    <t>7754807167307</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
+  </si>
+  <si>
+    <t>016788</t>
+  </si>
+  <si>
+    <t>7754807167888</t>
+  </si>
+  <si>
+    <t>VOLEY CUERO COSIDO CREW</t>
+  </si>
+  <si>
+    <t>016737</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR1</t>
+  </si>
+  <si>
+    <t>016738</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR2</t>
+  </si>
+  <si>
+    <t>016739</t>
+  </si>
+  <si>
+    <t>VOLEY CELULAR PWR3</t>
+  </si>
+  <si>
+    <t>016004</t>
+  </si>
+  <si>
+    <t>7754807160049</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPARTANO #3</t>
+  </si>
+  <si>
+    <t>015938</t>
+  </si>
+  <si>
+    <t>7754807159388</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA FREE #5</t>
+  </si>
+  <si>
+    <t>016678</t>
+  </si>
+  <si>
+    <t>7754807166782</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA URBAN #5</t>
+  </si>
+  <si>
+    <t>016724</t>
+  </si>
+  <si>
+    <t>7754807167246</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA SPECTRE #5</t>
+  </si>
+  <si>
+    <t>016783</t>
+  </si>
+  <si>
+    <t>7754807167833</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA INVICTUS  #5</t>
+  </si>
+  <si>
+    <t>014323</t>
+  </si>
+  <si>
+    <t>7754807143233</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES BLANCO #5</t>
+  </si>
+  <si>
+    <t>014796</t>
+  </si>
+  <si>
+    <t>7754807147965</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA TEAM #5</t>
+  </si>
+  <si>
+    <t>011883</t>
+  </si>
+  <si>
+    <t>7754807118835</t>
+  </si>
+  <si>
+    <t>FUTBOL GOMA PAISES COLORES #5</t>
+  </si>
+  <si>
+    <t>016657</t>
+  </si>
+  <si>
+    <t>7754807166577</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA BUTTERFLY</t>
+  </si>
+  <si>
+    <t>015936</t>
+  </si>
+  <si>
+    <t>7754807159364</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
+  </si>
+  <si>
+    <t>014268</t>
+  </si>
+  <si>
+    <t>7754807142687</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
+  </si>
+  <si>
+    <t>016784</t>
+  </si>
+  <si>
+    <t>7754807167840</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FLORES2</t>
+  </si>
+  <si>
+    <t>016786</t>
+  </si>
+  <si>
+    <t>7754807167864</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA FRUTAS2</t>
+  </si>
+  <si>
+    <t>015939</t>
+  </si>
+  <si>
+    <t>7754807159395</t>
+  </si>
+  <si>
+    <t>VOLEY VINIBALL GOMA FOLK</t>
+  </si>
+  <si>
+    <t>016785</t>
+  </si>
+  <si>
+    <t>7754807167857</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA MARIPOSAS</t>
+  </si>
+  <si>
+    <t>016787</t>
+  </si>
+  <si>
+    <t>7754807167871</t>
+  </si>
+  <si>
+    <t>VOLEY GOMA URBANA</t>
+  </si>
+  <si>
+    <t>016672</t>
+  </si>
+  <si>
+    <t>7754807166720</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 SONRISAS</t>
+  </si>
+  <si>
+    <t>014271</t>
+  </si>
+  <si>
+    <t>7754807142717</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #3 NARANJA</t>
+  </si>
+  <si>
+    <t>014270</t>
+  </si>
+  <si>
+    <t>7754807111638</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 NARANJA</t>
+  </si>
+  <si>
+    <t>014277</t>
+  </si>
+  <si>
+    <t>7754807142779</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 NARANJA</t>
+  </si>
+  <si>
+    <t>015933</t>
+  </si>
+  <si>
+    <t>7754807159333</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 PERU</t>
+  </si>
+  <si>
+    <t>016676</t>
+  </si>
+  <si>
+    <t>7754807166768</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 GALAXY</t>
+  </si>
+  <si>
+    <t>016675</t>
+  </si>
+  <si>
+    <t>7754807166751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 GALAXY</t>
+  </si>
+  <si>
+    <t>016752</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 LEGACY</t>
+  </si>
+  <si>
+    <t>016750</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 LEGACY</t>
+  </si>
+  <si>
+    <t>016751</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #5 JAM</t>
+  </si>
+  <si>
+    <t>016749</t>
+  </si>
+  <si>
+    <t>BASQUET GOMA #7 JAM</t>
+  </si>
+  <si>
+    <t>016764</t>
+  </si>
+  <si>
+    <t>BALONMANO GOMA #1</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>016727</t>
-  </si>
-  <si>
-    <t>7754807167277</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #5</t>
-  </si>
-  <si>
-    <t>016756</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA LEAGUE #4</t>
-  </si>
-  <si>
-    <t>016755</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PRESTIGE #5</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>016757</t>
-  </si>
-  <si>
-    <t>7754807167574</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #5</t>
-  </si>
-  <si>
-    <t>016760</t>
-  </si>
-  <si>
-    <t>7754807167604</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PERU #4</t>
-  </si>
-  <si>
-    <t>016758</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #5</t>
-  </si>
-  <si>
-    <t>016761</t>
-  </si>
-  <si>
-    <t>7754807167611</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA ARGENTINA #4</t>
-  </si>
-  <si>
-    <t>016759</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #5</t>
-  </si>
-  <si>
-    <t>016762</t>
-  </si>
-  <si>
-    <t>7754807167628</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BRASIL #4</t>
-  </si>
-  <si>
-    <t>016706</t>
-  </si>
-  <si>
-    <t>7754807167062</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA BLANQUIRROJA #5</t>
-  </si>
-  <si>
-    <t>016708</t>
-  </si>
-  <si>
-    <t>7754807167086</t>
-  </si>
-  <si>
-    <t>FUTBOL CUERO TERMOSELLADA PEGASUS #5</t>
-  </si>
-  <si>
-    <t>014375</t>
-  </si>
-  <si>
-    <t>7754807143752</t>
-  </si>
-  <si>
-    <t>FUTSAL CUERO VULC #3.5</t>
-  </si>
-  <si>
-    <t>016766</t>
-  </si>
-  <si>
-    <t>FUTSAL TERMOSELLADA ALEGRO</t>
-  </si>
-  <si>
-    <t>016767</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #5</t>
-  </si>
-  <si>
-    <t>016768</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER2 #5</t>
-  </si>
-  <si>
-    <t>016769</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER3 #5</t>
-  </si>
-  <si>
-    <t>016770</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER4 #5</t>
-  </si>
-  <si>
-    <t>016771</t>
-  </si>
-  <si>
-    <t>FUTBOL VULCANIZADA PREMIER1 #4</t>
-  </si>
-  <si>
-    <t>016743</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU PER2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016744</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU BRA2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016745</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU ARG2 CUP24 #5</t>
-  </si>
-  <si>
-    <t>016746</t>
-  </si>
-  <si>
-    <t>FUTBOL TPU FLAGS CUP24 #5</t>
-  </si>
-  <si>
-    <t>016747</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA1</t>
-  </si>
-  <si>
-    <t>016748</t>
-  </si>
-  <si>
-    <t>VOLEY PU LIGA2</t>
-  </si>
-  <si>
-    <t>016729</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FLORES</t>
-  </si>
-  <si>
-    <t>016731</t>
-  </si>
-  <si>
-    <t>VOLEY CUP CUERO COSIDO CELESTE AMARILLO ROSADO</t>
-  </si>
-  <si>
-    <t>016728</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK</t>
-  </si>
-  <si>
-    <t>016730</t>
-  </si>
-  <si>
-    <t>7754807167307</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO FOLK GRAFITTI</t>
-  </si>
-  <si>
-    <t>016788</t>
-  </si>
-  <si>
-    <t>7754807167888</t>
-  </si>
-  <si>
-    <t>VOLEY CUERO COSIDO CREW</t>
-  </si>
-  <si>
-    <t>016737</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR1</t>
-  </si>
-  <si>
-    <t>016738</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR2</t>
-  </si>
-  <si>
-    <t>016739</t>
-  </si>
-  <si>
-    <t>VOLEY CELULAR PWR3</t>
-  </si>
-  <si>
-    <t>016004</t>
-  </si>
-  <si>
-    <t>7754807160049</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPARTANO #3</t>
-  </si>
-  <si>
-    <t>015938</t>
-  </si>
-  <si>
-    <t>7754807159388</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA FREE #5</t>
-  </si>
-  <si>
-    <t>016678</t>
-  </si>
-  <si>
-    <t>7754807166782</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA URBAN #5</t>
-  </si>
-  <si>
-    <t>016724</t>
-  </si>
-  <si>
-    <t>7754807167246</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA SPECTRE #5</t>
-  </si>
-  <si>
-    <t>016783</t>
-  </si>
-  <si>
-    <t>7754807167833</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA INVICTUS  #5</t>
-  </si>
-  <si>
-    <t>014323</t>
-  </si>
-  <si>
-    <t>7754807143233</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES BLANCO #5</t>
-  </si>
-  <si>
-    <t>014796</t>
-  </si>
-  <si>
-    <t>7754807147965</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA TEAM #5</t>
-  </si>
-  <si>
-    <t>011883</t>
-  </si>
-  <si>
-    <t>7754807118835</t>
-  </si>
-  <si>
-    <t>FUTBOL GOMA PAISES COLORES #5</t>
-  </si>
-  <si>
-    <t>016657</t>
-  </si>
-  <si>
-    <t>7754807166577</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA BUTTERFLY</t>
-  </si>
-  <si>
-    <t>015936</t>
-  </si>
-  <si>
-    <t>7754807159364</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA MULTICOLOR</t>
-  </si>
-  <si>
-    <t>014268</t>
-  </si>
-  <si>
-    <t>7754807142687</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA TRICOLOR</t>
-  </si>
-  <si>
-    <t>016784</t>
-  </si>
-  <si>
-    <t>7754807167840</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FLORES2</t>
-  </si>
-  <si>
-    <t>016786</t>
-  </si>
-  <si>
-    <t>7754807167864</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA FRUTAS2</t>
-  </si>
-  <si>
-    <t>015939</t>
-  </si>
-  <si>
-    <t>7754807159395</t>
-  </si>
-  <si>
-    <t>VOLEY VINIBALL GOMA FOLK</t>
-  </si>
-  <si>
-    <t>016785</t>
-  </si>
-  <si>
-    <t>7754807167857</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA MARIPOSAS</t>
-  </si>
-  <si>
-    <t>016787</t>
-  </si>
-  <si>
-    <t>7754807167871</t>
-  </si>
-  <si>
-    <t>VOLEY GOMA URBANA</t>
-  </si>
-  <si>
-    <t>016672</t>
-  </si>
-  <si>
-    <t>7754807166720</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 SONRISAS</t>
-  </si>
-  <si>
-    <t>014271</t>
-  </si>
-  <si>
-    <t>7754807142717</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #3 NARANJA</t>
-  </si>
-  <si>
-    <t>014270</t>
-  </si>
-  <si>
-    <t>7754807111638</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 NARANJA</t>
-  </si>
-  <si>
-    <t>014277</t>
-  </si>
-  <si>
-    <t>7754807142779</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 NARANJA</t>
-  </si>
-  <si>
-    <t>015933</t>
-  </si>
-  <si>
-    <t>7754807159333</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 PERU</t>
-  </si>
-  <si>
-    <t>016676</t>
-  </si>
-  <si>
-    <t>7754807166768</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 GALAXY</t>
-  </si>
-  <si>
-    <t>016675</t>
-  </si>
-  <si>
-    <t>7754807166751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 GALAXY</t>
-  </si>
-  <si>
-    <t>016752</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 LEGACY</t>
-  </si>
-  <si>
-    <t>016750</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 LEGACY</t>
-  </si>
-  <si>
-    <t>016751</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #5 JAM</t>
-  </si>
-  <si>
-    <t>016749</t>
-  </si>
-  <si>
-    <t>BASQUET GOMA #7 JAM</t>
-  </si>
-  <si>
-    <t>016764</t>
-  </si>
-  <si>
-    <t>BALONMANO GOMA #1</t>
   </si>
   <si>
     <t>016765</t>
@@ -1712,12 +1712,12 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1740,12 +1740,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2196,11 +2196,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="2">
-        <v>2050</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,22 +2208,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="2">
-        <v>3800</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2265,11 +2265,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="2">
-        <v>606</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2288,11 +2288,11 @@
       <c r="E7">
         <v>24</v>
       </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
       </c>
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="2">
-        <v>4742</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2323,22 +2323,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
       </c>
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="2">
-        <v>1463</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2346,22 +2346,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="2">
-        <v>1496</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2369,22 +2369,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="2">
-        <v>180</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,22 +2392,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="2">
-        <v>1426</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,22 +2415,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
       </c>
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="2">
-        <v>168</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="2">
-        <v>182</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2461,22 +2461,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
       </c>
       <c r="E15">
         <v>36</v>
       </c>
       <c r="F15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2484,22 +2484,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
       </c>
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="2">
-        <v>1012</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2507,22 +2507,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>24</v>
       </c>
       <c r="F17" s="4">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2530,22 +2530,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>36</v>
       </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>23</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2553,22 +2553,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="2">
-        <v>3828</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2576,22 +2576,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="2">
-        <v>3206</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2599,22 +2599,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="2">
-        <v>8229</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2622,22 +2622,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="2">
-        <v>1330</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2645,22 +2645,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23">
         <v>48</v>
       </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,22 +2668,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2691,22 +2691,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2714,22 +2714,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26">
         <v>48</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2737,22 +2737,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>23</v>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2760,22 +2760,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>36</v>
       </c>
       <c r="F28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2783,22 +2783,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="2">
-        <v>3043</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2806,22 +2806,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>23</v>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2829,22 +2829,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>23</v>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2852,22 +2852,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>81</v>
       </c>
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="2">
-        <v>3505</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2875,22 +2875,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
         <v>82</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
       </c>
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="2">
-        <v>2922</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2898,22 +2898,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="2">
-        <v>263</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>10</v>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2921,22 +2921,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="2">
-        <v>518</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2944,22 +2944,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="2">
-        <v>873</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2967,22 +2967,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
         <v>91</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
       </c>
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="2">
-        <v>7641</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2990,22 +2990,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
         <v>94</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
       </c>
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="2">
-        <v>1483</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3013,22 +3013,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>99</v>
       </c>
       <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="6">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>23</v>
+      <c r="F39" s="4">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3036,22 +3036,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
       </c>
       <c r="E40">
         <v>48</v>
       </c>
-      <c r="F40" s="6">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>23</v>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>105</v>
       </c>
       <c r="E41">
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3082,22 +3082,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
         <v>106</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>107</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42" s="4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3105,22 +3105,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
         <v>109</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
       </c>
       <c r="E43">
         <v>48</v>
       </c>
-      <c r="F43" s="6">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>23</v>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3128,22 +3128,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
         <v>112</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>114</v>
       </c>
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="2">
-        <v>6524</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3151,22 +3151,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
         <v>115</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>116</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
       </c>
       <c r="E45">
         <v>48</v>
       </c>
-      <c r="F45" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>23</v>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3174,22 +3174,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" t="s">
         <v>118</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
       </c>
       <c r="E46">
         <v>48</v>
       </c>
-      <c r="F46" s="6">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>23</v>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3197,22 +3197,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
         <v>121</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>122</v>
-      </c>
-      <c r="D47" t="s">
-        <v>123</v>
       </c>
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="2">
-        <v>11965</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3220,22 +3220,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" t="s">
         <v>124</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>125</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
       </c>
       <c r="E48">
         <v>48</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>23</v>
+      <c r="F48" s="4">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3243,22 +3243,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
         <v>127</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>128</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
       </c>
       <c r="E49">
         <v>48</v>
       </c>
       <c r="F49" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3266,22 +3266,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
         <v>130</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>131</v>
-      </c>
-      <c r="D50" t="s">
-        <v>132</v>
       </c>
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="2">
-        <v>5578</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3289,22 +3289,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
         <v>133</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>134</v>
-      </c>
-      <c r="D51" t="s">
-        <v>135</v>
       </c>
       <c r="E51">
         <v>48</v>
       </c>
-      <c r="F51" s="6">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>23</v>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3312,22 +3312,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
         <v>136</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>137</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
       </c>
       <c r="E52">
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3335,22 +3335,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" t="s">
         <v>139</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>140</v>
-      </c>
-      <c r="D53" t="s">
-        <v>141</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
       <c r="F53" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3358,22 +3358,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" t="s">
         <v>142</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>143</v>
-      </c>
-      <c r="D54" t="s">
-        <v>144</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54" s="4">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3381,22 +3381,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
       </c>
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="2">
-        <v>1955</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3404,22 +3404,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" t="s">
         <v>148</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>149</v>
-      </c>
-      <c r="D56" t="s">
-        <v>150</v>
       </c>
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="2">
-        <v>196</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3427,22 +3427,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
         <v>151</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>152</v>
-      </c>
-      <c r="D57" t="s">
-        <v>153</v>
       </c>
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="2">
-        <v>2190</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="F57" s="4">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" t="s">
         <v>154</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>155</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
       </c>
       <c r="E58">
         <v>36</v>
       </c>
-      <c r="F58" s="6">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>23</v>
+      <c r="F58" s="4">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" t="s">
         <v>157</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>158</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
       </c>
       <c r="E59">
         <v>36</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>23</v>
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3496,22 +3496,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="2">
-        <v>1377</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="F60" s="4">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3519,22 +3519,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61">
         <v>36</v>
       </c>
-      <c r="F61" s="6">
-        <v>0</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>23</v>
+      <c r="F61" s="4">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3542,22 +3542,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="2">
-        <v>915</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3565,22 +3565,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="2">
-        <v>798</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3588,22 +3588,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="2">
-        <v>418</v>
-      </c>
-      <c r="G64" s="3" t="s">
+      <c r="F64" s="6">
         <v>10</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3622,11 +3622,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="2">
-        <v>1218</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,11 +3645,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="2">
-        <v>5188</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3668,11 +3668,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="2">
-        <v>1226</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="F67" s="4">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3691,11 +3691,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="2">
-        <v>2119</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3714,11 +3714,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="2">
-        <v>1118</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>10</v>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3737,11 +3737,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="2">
-        <v>4180</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3760,11 +3760,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="2">
-        <v>5085</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3783,11 +3783,11 @@
       <c r="E72">
         <v>60</v>
       </c>
-      <c r="F72" s="6">
-        <v>0</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>23</v>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3806,11 +3806,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="2">
-        <v>3198</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3829,11 +3829,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="2">
-        <v>1302</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3852,11 +3852,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="2">
-        <v>4399</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>10</v>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3875,11 +3875,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="2">
-        <v>8596</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3898,11 +3898,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="2">
-        <v>3977</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3921,11 +3921,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="2">
-        <v>6465</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3944,11 +3944,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="2">
-        <v>5202</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3968,10 +3968,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3991,10 +3991,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4013,11 +4013,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="2">
-        <v>1124</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>10</v>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4036,11 +4036,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="2">
-        <v>1037</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4059,11 +4059,11 @@
       <c r="E84">
         <v>60</v>
       </c>
-      <c r="F84" s="6">
-        <v>0</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>23</v>
+      <c r="F84" s="4">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="F85" s="4">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4105,11 +4105,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="2">
-        <v>333</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="F86" s="4">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4128,11 +4128,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="2">
-        <v>1531</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="F87" s="4">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4151,11 +4151,11 @@
       <c r="E88">
         <v>60</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>23</v>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4174,11 +4174,11 @@
       <c r="E89">
         <v>60</v>
       </c>
-      <c r="F89" s="6">
-        <v>0</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>23</v>
+      <c r="F89" s="4">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4197,11 +4197,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="2">
-        <v>734</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="F90" s="4">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4220,11 +4220,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="2">
-        <v>1518</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>10</v>
+      <c r="F91" s="4">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4243,11 +4243,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="2">
-        <v>1372</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4266,11 +4266,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="2">
-        <v>1251</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>10</v>
+      <c r="F93" s="4">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4289,11 +4289,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="2">
-        <v>1399</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>10</v>
+      <c r="F94" s="4">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4335,11 +4335,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="2">
-        <v>2485</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="F96" s="4">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,11 +4358,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="2">
-        <v>5025</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4381,11 +4381,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="2">
-        <v>3434</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4404,11 +4404,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="2">
-        <v>3915</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="F99" s="4">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4427,11 +4427,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="2">
-        <v>1544</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>10</v>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4450,11 +4450,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="2">
-        <v>5802</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>10</v>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4473,11 +4473,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="2">
-        <v>3253</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="F102" s="4">
+        <v>0</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4496,11 +4496,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="2">
-        <v>1816</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4519,11 +4519,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="2">
-        <v>368</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4542,11 +4542,11 @@
       <c r="E105">
         <v>60</v>
       </c>
-      <c r="F105" s="6">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>23</v>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,11 +4565,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="2">
-        <v>852</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4588,11 +4588,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="2">
-        <v>5594</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4611,11 +4611,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="2">
-        <v>1998</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>0</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4634,11 +4634,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="2">
-        <v>1725</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4657,11 +4657,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="2">
-        <v>1887</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4680,11 +4680,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="2">
-        <v>6130</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="F111" s="4">
+        <v>0</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4703,11 +4703,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="2">
-        <v>7112</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4726,11 +4726,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="2">
-        <v>6610</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="F113" s="4">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4749,11 +4749,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="2">
-        <v>11151</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="F114" s="4">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4772,11 +4772,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="2">
-        <v>239</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4795,11 +4795,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="2">
-        <v>85</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4818,11 +4818,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="2">
-        <v>273</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>0</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4841,11 +4841,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="2">
-        <v>272</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>10</v>
+      <c r="F118" s="4">
+        <v>0</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,11 +4864,11 @@
       <c r="E119">
         <v>12</v>
       </c>
-      <c r="F119" s="6">
-        <v>0</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>23</v>
+      <c r="F119" s="4">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,11 +4887,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="2">
-        <v>261</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>0</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,11 +4910,11 @@
       <c r="E121">
         <v>36</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>23</v>
+      <c r="F121" s="4">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,11 +4933,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="2">
-        <v>2925</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="F122" s="4">
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>36</v>
       </c>
       <c r="F123" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="2">
-        <v>2515</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>10</v>
+      <c r="F124" s="4">
+        <v>0</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,11 +5002,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="2">
-        <v>969</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="F125" s="4">
+        <v>0</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,11 +5025,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="2">
-        <v>2200</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5049,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="F127" s="4">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -5072,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="2">
-        <v>1067</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5117,11 +5117,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="2">
-        <v>884</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>0</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5141,10 +5141,10 @@
         <v>120</v>
       </c>
       <c r="F131" s="4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5164,10 +5164,10 @@
         <v>120</v>
       </c>
       <c r="F132" s="4">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5186,11 +5186,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="2">
-        <v>6592</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5209,11 +5209,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="2">
-        <v>1017</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>10</v>
+      <c r="F134" s="4">
+        <v>0</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5233,10 +5233,10 @@
         <v>120</v>
       </c>
       <c r="F135" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,11 +5255,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="2">
-        <v>4015</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>10</v>
+      <c r="F136" s="4">
+        <v>0</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,11 +5278,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="2">
-        <v>1904</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="F137" s="4">
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>120</v>
       </c>
       <c r="F138" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,11 +5324,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="2">
-        <v>4463</v>
-      </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="F139" s="4">
+        <v>0</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5348,10 +5348,10 @@
         <v>120</v>
       </c>
       <c r="F140" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,11 +5370,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="2">
-        <v>4217</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>0</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,11 +5393,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="2">
-        <v>3364</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>0</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5417,10 +5417,10 @@
         <v>120</v>
       </c>
       <c r="F143" s="4">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,11 +5439,11 @@
       <c r="E144">
         <v>120</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>23</v>
+      <c r="F144" s="4">
+        <v>0</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5463,10 +5463,10 @@
         <v>120</v>
       </c>
       <c r="F145" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5485,11 +5485,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="2">
-        <v>752</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>0</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5508,11 +5508,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="2">
-        <v>1964</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="F147" s="4">
+        <v>0</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5532,10 +5532,10 @@
         <v>120</v>
       </c>
       <c r="F148" s="4">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5555,10 +5555,10 @@
         <v>120</v>
       </c>
       <c r="F149" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5578,10 +5578,10 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -5600,11 +5600,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="2">
-        <v>2007</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>10</v>
+      <c r="F151" s="4">
+        <v>0</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>120</v>
       </c>
       <c r="F152" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5646,11 +5646,11 @@
       <c r="E153">
         <v>120</v>
       </c>
-      <c r="F153" s="6">
-        <v>0</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>23</v>
+      <c r="F153" s="4">
+        <v>0</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5669,11 +5669,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>3277</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>0</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5692,11 +5692,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="2">
-        <v>908</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>10</v>
+      <c r="F155" s="4">
+        <v>0</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -5716,10 +5716,10 @@
         <v>120</v>
       </c>
       <c r="F156" s="4">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5738,11 +5738,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="2">
-        <v>3114</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>0</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="2">
-        <v>1101</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>0</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5784,11 +5784,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>3978</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5808,10 +5808,10 @@
         <v>120</v>
       </c>
       <c r="F160" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5830,11 +5830,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="2">
-        <v>1926</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5853,11 +5853,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="2">
-        <v>4672</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>0</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5876,11 +5876,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="2">
-        <v>4562</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>0</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5900,10 +5900,10 @@
         <v>120</v>
       </c>
       <c r="F164" s="4">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5922,11 +5922,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="2">
-        <v>1260</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>0</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5945,11 +5945,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="2">
-        <v>3735</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>0</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5968,11 +5968,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="2">
-        <v>764</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>0</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5992,10 +5992,10 @@
         <v>120</v>
       </c>
       <c r="F168" s="4">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -6014,11 +6014,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="2">
-        <v>703</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -6037,11 +6037,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="6">
-        <v>0</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>23</v>
+      <c r="F170" s="4">
+        <v>0</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6060,11 +6060,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="2">
-        <v>7702</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>10</v>
+      <c r="F171" s="4">
+        <v>0</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -6083,11 +6083,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="2">
-        <v>2089</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -6106,11 +6106,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="2">
-        <v>232</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>0</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6129,11 +6129,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="2">
-        <v>147</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6175,11 +6175,11 @@
       <c r="E176">
         <v>12</v>
       </c>
-      <c r="F176" s="6">
-        <v>0</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>23</v>
+      <c r="F176" s="4">
+        <v>0</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6198,11 +6198,11 @@
       <c r="E177">
         <v>12</v>
       </c>
-      <c r="F177" s="6">
-        <v>0</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>23</v>
+      <c r="F177" s="4">
+        <v>0</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6221,11 +6221,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="2">
-        <v>163</v>
-      </c>
-      <c r="G178" s="3" t="s">
-        <v>10</v>
+      <c r="F178" s="4">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6245,10 +6245,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6267,11 +6267,11 @@
       <c r="E180">
         <v>12</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>23</v>
+      <c r="F180" s="4">
+        <v>0</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6290,11 +6290,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
-        <v>0</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>23</v>
+      <c r="F181" s="4">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6313,11 +6313,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="2">
-        <v>211</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>0</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="F183" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -6360,10 +6360,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -6382,11 +6382,11 @@
       <c r="E185">
         <v>12</v>
       </c>
-      <c r="F185" s="2">
-        <v>3022</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="F185" s="4">
+        <v>0</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6405,11 +6405,11 @@
       <c r="E186">
         <v>12</v>
       </c>
-      <c r="F186" s="2">
-        <v>286</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6428,11 +6428,11 @@
       <c r="E187">
         <v>12</v>
       </c>
-      <c r="F187" s="2">
-        <v>157</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>0</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6451,11 +6451,11 @@
       <c r="E188">
         <v>12</v>
       </c>
-      <c r="F188" s="2">
-        <v>654</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>0</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6475,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="F189" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6497,11 +6497,11 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190" s="2">
-        <v>1156</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>10</v>
+      <c r="F190" s="4">
+        <v>0</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -6520,11 +6520,11 @@
       <c r="E191">
         <v>18</v>
       </c>
-      <c r="F191" s="2">
-        <v>1901</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>10</v>
+      <c r="F191" s="4">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -6543,11 +6543,11 @@
       <c r="E192">
         <v>12</v>
       </c>
-      <c r="F192" s="2">
-        <v>1913</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>10</v>
+      <c r="F192" s="4">
+        <v>0</v>
+      </c>
+      <c r="G192" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -6566,11 +6566,11 @@
       <c r="E193">
         <v>400</v>
       </c>
-      <c r="F193" s="2">
-        <v>76950</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>10</v>
+      <c r="F193" s="4">
+        <v>0</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -6589,11 +6589,11 @@
       <c r="E194">
         <v>400</v>
       </c>
-      <c r="F194" s="2">
-        <v>72165</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>10</v>
+      <c r="F194" s="4">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -6612,11 +6612,11 @@
       <c r="E195">
         <v>120</v>
       </c>
-      <c r="F195" s="2">
-        <v>3620</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>10</v>
+      <c r="F195" s="4">
+        <v>0</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6635,11 +6635,11 @@
       <c r="E196">
         <v>120</v>
       </c>
-      <c r="F196" s="2">
-        <v>1816</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>10</v>
+      <c r="F196" s="4">
+        <v>0</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -6658,11 +6658,11 @@
       <c r="E197">
         <v>120</v>
       </c>
-      <c r="F197" s="2">
-        <v>8964</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>10</v>
+      <c r="F197" s="4">
+        <v>0</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -6681,11 +6681,11 @@
       <c r="E198">
         <v>120</v>
       </c>
-      <c r="F198" s="6">
-        <v>0</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>23</v>
+      <c r="F198" s="4">
+        <v>0</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -6704,11 +6704,11 @@
       <c r="E199">
         <v>120</v>
       </c>
-      <c r="F199" s="2">
-        <v>8040</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+      <c r="F199" s="4">
+        <v>0</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -4198,7 +4198,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4312,11 +4312,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>23</v>
+      <c r="F95" s="4">
+        <v>1</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1483</v>
+        <v>1435</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3071,7 +3071,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>15</v>
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6499</v>
+        <v>6450</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11847</v>
+        <v>11798</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>5570</v>
+        <v>5474</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3346,11 +3346,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="4">
-        <v>5</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>15</v>
+      <c r="F53" s="2">
+        <v>294</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3393,7 +3393,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="2">
-        <v>2218</v>
+        <v>2182</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -3669,7 +3669,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="2">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1299</v>
+        <v>1269</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="2">
-        <v>4399</v>
+        <v>4369</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3945,7 +3945,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="2">
-        <v>5202</v>
+        <v>5172</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -4014,7 +4014,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="2">
-        <v>1124</v>
+        <v>1094</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="2">
-        <v>1369</v>
+        <v>1349</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4267,7 +4267,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="2">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4290,7 +4290,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="2">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="2">
-        <v>2485</v>
+        <v>2455</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="2">
-        <v>3432</v>
+        <v>3401</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>1543</v>
+        <v>1513</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="2">
-        <v>2999</v>
+        <v>2969</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>1728</v>
+        <v>1668</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -4704,7 +4704,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="2">
-        <v>7097</v>
+        <v>7067</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>10</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="2">
-        <v>6609</v>
+        <v>6549</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11106</v>
+        <v>11076</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5347,11 +5347,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="6">
-        <v>0</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>23</v>
+      <c r="F140" s="2">
+        <v>870</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5486,7 +5486,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="2">
-        <v>743</v>
+        <v>683</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>10</v>
@@ -6037,11 +6037,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="6">
-        <v>0</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>23</v>
+      <c r="F170" s="4">
+        <v>43</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>76950</v>
+        <v>76550</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>72165</v>
+        <v>71765</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11798</v>
+        <v>11797</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>120</v>
       </c>
       <c r="F195" s="2">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6450</v>
+        <v>6447</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -3140,7 +3140,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="2">
-        <v>6447</v>
+        <v>6183</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -3416,7 +3416,7 @@
         <v>36</v>
       </c>
       <c r="F56" s="4">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>15</v>
@@ -3508,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="2">
-        <v>1375</v>
+        <v>1351</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -3967,11 +3967,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>11</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>15</v>
+      <c r="F80" s="6">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4014,7 +4014,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="2">
-        <v>1094</v>
+        <v>938</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="2">
-        <v>1517</v>
+        <v>1433</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4566,7 +4566,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="2">
-        <v>1458</v>
+        <v>1386</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>10</v>
@@ -4635,7 +4635,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="2">
-        <v>1668</v>
+        <v>1644</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         <v>12</v>
       </c>
       <c r="F186" s="2">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>18</v>
       </c>
       <c r="F191" s="2">
-        <v>1901</v>
+        <v>1865</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6567,7 +6567,7 @@
         <v>400</v>
       </c>
       <c r="F193" s="2">
-        <v>76550</v>
+        <v>75750</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="F194" s="2">
-        <v>71765</v>
+        <v>70965</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5341</v>
+        <v>5335</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2922</v>
+        <v>2916</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1435</v>
+        <v>1387</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11797</v>
+        <v>11773</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>3194</v>
+        <v>3182</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8593</v>
+        <v>8545</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3967,11 +3967,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="6">
-        <v>0</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>23</v>
+      <c r="F80" s="4">
+        <v>72</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3914</v>
+        <v>3854</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>5577</v>
+        <v>5517</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11076</v>
+        <v>11016</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>519</v>
+        <v>483</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>4217</v>
+        <v>4133</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4672</v>
+        <v>4660</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7702</v>
+        <v>7678</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5335</v>
+        <v>5329</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2679,11 +2679,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2702,11 +2702,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2916</v>
+        <v>2910</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11773</v>
+        <v>11761</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3324,7 +3324,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="4">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>15</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8545</v>
+        <v>8533</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>15</v>
@@ -4405,7 +4405,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="2">
-        <v>3854</v>
+        <v>3842</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="2">
-        <v>5517</v>
+        <v>5505</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>11016</v>
+        <v>11004</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="2">
-        <v>4133</v>
+        <v>4127</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>10</v>
@@ -5854,7 +5854,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="2">
-        <v>4660</v>
+        <v>4648</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -6084,7 +6084,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="2">
-        <v>2065</v>
+        <v>2053</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_PELOTAS.xlsx
+++ b/frontend/public/reports/StockPulse_PELOTAS.xlsx
@@ -2197,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="2">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>5323</v>
+        <v>5320</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="2">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>3504</v>
+        <v>3498</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="2">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="2">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="2">
-        <v>11737</v>
+        <v>11731</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="2">
-        <v>5474</v>
+        <v>5468</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -3439,7 +3439,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="2">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3807,7 +3807,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="2">
-        <v>3170</v>
+        <v>3152</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="2">
-        <v>1221</v>
+        <v>1203</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="2">
-        <v>8509</v>
+        <v>8491</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="4">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>15</v>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="2">
-        <v>1513</v>
+        <v>1495</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4750,7 +4750,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2">
-        <v>10980</v>
+        <v>10968</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="2">
-        <v>2508</v>
+        <v>2460</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="4">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>15</v>
@@ -5578,7 +5578,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="4">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="G150" s="5" t="s">
         <v>15</v>
@@ -5601,7 +5601,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="2">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5670,7 +5670,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="2">
-        <v>3277</v>
+        <v>3265</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
@@ -5807,11 +5807,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="4">
-        <v>6</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>15</v>
+      <c r="F160" s="6">
+        <v>0</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5831,7 +5831,7 @@
         <v>120</v>
       </c>
       <c r="F161" s="2">
-        <v>1926</v>
+        <v>1914</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>7666</v>
+        <v>7654</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="2">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>10</v>
